--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code for experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382F0F31-B8F3-46F5-A042-496E9B53E5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A35E41-5FC3-42EA-BF11-95C41BF28EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="demand" sheetId="1" r:id="rId1"/>
@@ -29753,7 +29753,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F1465" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -37114,7 +37113,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F367" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -44475,7 +44473,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F367" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -51836,7 +51833,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F367" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -59197,7 +59193,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F367" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -73875,7 +73870,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F733" xr:uid="{994559CB-BF25-4E1F-B609-36E21E36A940}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -73888,7 +73882,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="17" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -81233,7 +81227,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F367" xr:uid="{994559CB-BF25-4E1F-B609-36E21E36A940}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -88590,7 +88583,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F367" xr:uid="{994559CB-BF25-4E1F-B609-36E21E36A940}"/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code for experiment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60A35E41-5FC3-42EA-BF11-95C41BF28EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29610513-B596-4F4B-A11D-7D07B494F465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="demand" sheetId="1" r:id="rId1"/>
@@ -29765,7 +29765,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="21.77734375" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
@@ -37124,8 +37124,7 @@
   <dimension ref="A1:F367"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" customWidth="1"/>
+    <col min="1" max="2" width="13.88671875" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
@@ -44485,7 +44484,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" customWidth="1"/>
+    <col min="2" max="2" width="18.21875" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
@@ -51845,7 +51844,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="37.44140625" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
     <col min="4" max="4" width="11.33203125" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" customWidth="1"/>
@@ -59205,7 +59204,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="24.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -73882,7 +73881,7 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="17" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -81238,7 +81237,8 @@
   <dimension ref="A1:F367"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.88671875" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" customWidth="1"/>
   </cols>
   <sheetData>
